--- a/content/ui_text.xlsx
+++ b/content/ui_text.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>캐릭터를 선택하세요</t>
+          <t>캐릭터를 선택하세요.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>포스터에서 답을 찾아 옆에 적힌 세 자리 숫자를 입력하세요.</t>
+          <t>포스터에서 답을 찾아 세 자리 숫자를 입력하세요.</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>판 맨 위. 2026-09-19 확정</t>
+          <t>판 맨 위. 2026-09-19 확정 · 2026-09-26 「옆에 적힌」 뺌(사용자)</t>
         </is>
       </c>
     </row>
@@ -2387,6 +2387,816 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>📜 국가유산청 원문 두 대목</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>U-01</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 육조거리 튜토리얼</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>조작키 바로 위 가운데 한 줄 — 1단계(▲만 켜짐)</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>▲를 누르면 앞으로 이동합니다.</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ▲는 발화에서 빠져 있어 넣음 → 🙋 "맞아")</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>U-02</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 육조거리 튜토리얼</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>조작키 바로 위 가운데 한 줄 — 2단계(◀만 켜짐)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>◀를 눌러 왼쪽 대문 앞으로 이동하세요.</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ◀는 내가 넣음 → 🙋 "맞아")</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>U-03</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 육조거리 튜토리얼</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>조작키 바로 위 가운데 한 줄 — 연습 판이 걷힌 뒤(▲◀▶ 모두)</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>이제 광화문 앞으로 이동하세요.</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>U-04</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>연습 판 · 점검 퀴즈 자리</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>설명 글(위) — 아래 태블릿 그림(왼쪽)·포스터 그림(오른쪽)·닫기 B-08</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>광화문부터는 단어를 완성한 뒤, 퀴즈를 풀어야 합니다. 포스터에서 정답을 찾아서 세 자리 숫자를 입력하세요.</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장 · 낙관 없이 판이 걷힌다</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>U-05</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 육조거리 튜토리얼</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 실마리를 누르고 지도로 돌아왔을 때</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 관청의 대문 중 하나에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장 · 실마리는 오른쪽 위 관청 대문 한 곳에서만</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>U-06</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 실마리 곳(튜토리얼 · 본편)</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈)</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>이 문제를 맞히면 실마리가 하나 풀릴 것이오!</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장의 「풀면」→「맞히면」 → 🙋 "좋아" · 튜토리얼에서 확정 · 본편 곳 19개(U-12~U-30)에서도 같은 글 — 🙋 2026-09-25 "응 좋아." (담장·개울가는 말하는 이가 없어도 됨 · 튜토리얼 관청 대문과 같다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>U-07</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정전 앞마당</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 근정전 알림창(M5)을 닫은 뒤</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>아직 쓰지 않은 실마리가 있습니다. 품계석 앞 관리들에게 차례로 다가가 남은 실마리 문제를 모두 풀면 사정문으로 갈 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>U-08</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정전 앞마당</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 처음과 한 관리를 마칠 때마다</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>이제 {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}=왼쪽/오른쪽 · {n}=첫/두/세/네 — 코드가 바꿔 넣는다(예: 이제 왼쪽 줄 첫 번째 관리에게 가 보세요.) · 첫 번째 = 들어선 쪽(아래)에서 가장 가까운 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>U-09</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정전 앞마당</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈) — 관리에게 닿았을 때</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>남겨 둔 실마리가 있구려. 이 문제를 맞혀 보시오!</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정전 앞마당</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 다 풀기 전에 사정문 쪽 길목에 닿아 막혔을 때</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>아직 풀지 않은 실마리 문제가 남아 있습니다. {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}·{n}은 U-08과 같다(예: 오른쪽 줄 두 번째)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>U-11</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정전 앞마당</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>조작키 바로 위 가운데 한 줄(U-03 자리) — 마지막 문제를 맞혀 낙관(L-01)이 찍힌 뒤</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>모든 실마리를 풀었습니다. 이제 사정문으로 이동하세요.</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>U-12</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 광화문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 아래 분홍 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>U-13</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 광화문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 아래 지팡이를 든 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>U-14</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 광화문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 파란 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>U-15</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 홍례문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>U-16</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 홍례문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 남색 치마를 입은 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>U-17</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 홍례문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>U-18</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 영제교 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>U-19</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 영제교 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>U-20</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 영제교 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>U-21</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 영제교 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 개울가에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>U-22</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>U-23</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>U-24</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 파란 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>U-25</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>U-26</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 근정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 5번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 5</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>U-27</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 아래 남색 치마를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>U-28</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>U-29</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>U-30</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>왼쪽 노란 저고리를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
         </is>
       </c>
     </row>

--- a/content/ui_text.xlsx
+++ b/content/ui_text.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>아래 셋은 엑셀로 관리하지 않고 코드에 둔다(2026-09-18 합의 · B-11은 2026-09-22). 글자가 아니라 표시이고, 누르는 키와 짝을 이룬다.</t>
+          <t>아래 넷은 엑셀로 관리하지 않고 코드에 둔다(2026-09-18 합의 · B-11은 2026-09-22 · B-12는 2026-09-26). 글자가 아니라 표시이고, 누르는 키와 짝을 이루거나 코드가 세어 적는 숫자다.</t>
         </is>
       </c>
     </row>
@@ -582,18 +582,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>판 왼쪽 위 「2 / 3」 — 숫자만(말 없음 · 테두리 없는 글자 · 실마리 글씨와 같은 크기). 자모 조합 판 = 이 문에서 몇 번째 판(광화문도 「1 / 1」) · 힌트 퀴즈 판 = 이 자모 판의 실마리 가운데 몇 번째 · 근정전 = 여기서 풀 남은 실마리 문제 가운데 몇 번째. 코드가 그 판의 수로 세어 적는다 (기5 · 기6)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>갱신</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -608,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1475,61 +1487,61 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>문 앞 · 퀴즈</t>
+          <t>근정전 앞마당 · 힌트 퀴즈 판</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>정답 낙관의 글</t>
+          <t>판 맨 위 머리 안내(Q-03 자리 · 근정전에서만 Q-03 대신)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>앞에서 풀지 않은 실마리 문제입니다. 모두 맞히면 사정문으로 갈 수 있습니다.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>점검 퀴즈를 맞히면 판 한가운데 크게 찍힌다. 2026-09-19 확정</t>
+          <t>2026-09-26 📝 초안 → 🙋 "초안으로 할게 대신 줄바꿈해줘." — 화면에서 문장마다 한 줄(두 줄). 근정전 문제는 맞혀도 자모가 채워지지 않아 Q-03이 맞지 않는다(🙋 "근정전 앞마당에서 힌트를 풀 때는 정답을 맞히면 자음 혹은 모음 하나가 공개됩니다. 라는 지시문을 바꿔야 할 것 같아.")</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>사정전 · 알현</t>
+          <t>문 앞 · 퀴즈</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>세종의 첫 말 (자막)</t>
+          <t>정답 낙관의 글</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>어서 오너라.</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21) · 화면 차례는 S-08 → S-07 → S-09</t>
+          <t>점검 퀴즈를 맞히면 판 한가운데 크게 찍힌다. 2026-09-19 확정</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>S-07</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1539,24 +1551,24 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>플레이어의 말</t>
+          <t>세종의 첫 말 (자막)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>한글을 만들어주셔서 감사합니다.</t>
+          <t>어서 오너라.</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21 「창제해 주셔서」에서 바뀜)</t>
+          <t>🙋 사용자 문장 (2026-09-21) · 화면 차례는 S-08 → S-07 → S-09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,78 +1578,78 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>세종의 마지막 말 (자막)</t>
+          <t>플레이어의 말</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>한글을 많이 아껴 다오.</t>
+          <t>한글을 만들어주셔서 감사합니다.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21) · 이 말 뒤 게임이 끝난다</t>
+          <t>🙋 사용자 문장 (2026-09-21 「창제해 주셔서」에서 바뀜)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>N-01</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>끝 · 갈무리 판</t>
+          <t>사정전 · 알현</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>판 타이틀</t>
+          <t>세종의 마지막 말 (자막)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>갈무리</t>
+          <t>한글을 많이 아껴 다오.</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>📝 내 안 · 🙋 승인 (2026-09-21) · 표준국어대사전 「물건 따위를 잘 정리하거나 간수함」 · 문장 11장에만 붙는다(서약서 판에는 없다)</t>
+          <t>🙋 사용자 문장 (2026-09-21) · 이 말 뒤 게임이 끝난다</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>N-01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>끝 · 서약서 판</t>
+          <t>끝 · 갈무리 판</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>판 타이틀</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>서약서</t>
+          <t>갈무리</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 🙋 승인 (2026-09-21) · 띄어 보이는 것은 글자 간격(디자인)</t>
+          <t>📝 내 안 · 🙋 승인 (2026-09-21) · 표준국어대사전 「물건 따위를 잘 정리하거나 간수함」 · 문장 11장에만 붙는다(서약서 판에는 없다)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1647,24 +1659,24 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>요지</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>나는 세종대왕께서 만드신 한글을 아끼고 아름답게 사용하겠습니다.</t>
+          <t>서약서</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 뜻은 🙋 사용자 「한글을 아끼고 아름답게 사용하겠다」 · 승인</t>
+          <t>📝 내 초안 · 🙋 승인 (2026-09-21) · 띄어 보이는 것은 글자 간격(디자인)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>O-02</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1674,24 +1686,24 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>조항 1</t>
+          <t>요지</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>하나, 맞춤법을 지키며 바르게 쓰겠습니다.</t>
+          <t>나는 세종대왕께서 만드신 한글을 아끼고 아름답게 사용하겠습니다.</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장</t>
+          <t>📝 내 초안 · 뜻은 🙋 사용자 「한글을 아끼고 아름답게 사용하겠다」 · 승인</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1701,24 +1713,24 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>조항 2</t>
+          <t>조항 1</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>하나, 남을 아프게 하는 말 대신 고운 말을 쓰겠습니다.</t>
+          <t>하나, 맞춤법을 지키며 바르게 쓰겠습니다.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 🙋 "이건 좋아."</t>
+          <t>🙋 사용자 문장</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-04</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1728,24 +1740,24 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>조항 3</t>
+          <t>조항 2</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>하나, 한글이 만들어진 뜻을 기억하며 소중히 여기겠습니다.</t>
+          <t>하나, 남을 아프게 하는 말 대신 고운 말을 쓰겠습니다.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안(넷째 안) · 🙋 "응 지금 걸로 하자."</t>
+          <t>📝 내 초안 · 🙋 "이건 좋아."</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1755,24 +1767,24 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>체크 칸 글</t>
+          <t>조항 3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>위와 같이 서약합니다.</t>
+          <t>하나, 한글이 만들어진 뜻을 기억하며 소중히 여기겠습니다.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>🙋 "위와 같이 서약합니다. 좋아." · 체크하면 게임이 끝난다</t>
+          <t>📝 내 초안(넷째 안) · 🙋 "응 지금 걸로 하자."</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1782,24 +1794,24 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>체크 칸 글</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>(플레이한 날짜)</t>
+          <t>위와 같이 서약합니다.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>🙋 "날짜가 플레이하는 날로 나타나는 것도 좋아." · 🛠 기기 날짜로 채운다 · 서약서 판이 뜨는 날을 찍는다(🙋 "그렇게 해." 2026-09-22) · 꼴은 「2026년 9월 21일」(🙋 "지금 상태가 좋아." 2026-09-22)</t>
+          <t>🙋 "위와 같이 서약합니다. 좋아." · 체크하면 게임이 끝난다</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>B-09</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1809,24 +1821,24 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>저장 버튼</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(플레이한 날짜)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 왼쪽 · 누르면 갈무리 11장 + 서약서를 PDF로 내려받는다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+          <t>🙋 "날짜가 플레이하는 날로 나타나는 것도 좋아." · 🛠 기기 날짜로 채운다 · 서약서 판이 뜨는 날을 찍는다(🙋 "그렇게 해." 2026-09-22) · 꼴은 「2026년 9월 21일」(🙋 "지금 상태가 좋아." 2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>B-10</t>
+          <t>B-09</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1836,105 +1848,105 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>종료 버튼</t>
+          <t>저장 버튼</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 오른쪽 · 누르면 책상에 엎드려 잠든 모습으로 간다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 왼쪽 · 누르면 갈무리 11장 + 서약서를 PDF로 내려받는다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>끝 · 서약서 판</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>종료 버튼</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>종료</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 오른쪽 · 누르면 책상에 엎드려 잠든 모습으로 간다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>F-01</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>끝 · 저장</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>내려받는 PDF 파일 이름</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>세종대왕을 알현하라!</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>뒤에 .pdf를 붙인다 · 🙋 "그냥 세종대왕을 알현하라! 이걸로 하자." (2026-09-22) · T-01과 같은 글</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>B-08</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>문 앞 · 알림창</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>닫기 버튼</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>닫기</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-09-21 🙋 "닫기로 해."</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>M1-a</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>문 앞 · 광화문 알림창</t>
+          <t>문 앞 · 알림창</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>닫기 버튼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>광화문(光化門)</t>
+          <t>닫기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>2026-09-21 🙋 "닫기로 해."</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>M1-b</t>
+          <t>M1-a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1944,24 +1956,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>'광화'는 '군주에 의한 덕화(德化)'라는 뜻이다. 임금이 덕으로 사람들의 마음을 좋은 쪽으로 바꾼다는 말이다.</t>
+          <t>광화문(光化門)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>📜 앞 문장 국가유산청 원문 / 뒷 문장은 표준국어대사전 덕화·감화를 이어 푼 것</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>M1-c</t>
+          <t>M1-b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1971,51 +1983,51 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>광화문은 경복궁의 정문으로 3개의 홍예문으로 이루어져 있는데, 중앙의 홍예문은 왕이 드나들었고 좌우의 홍예문은 왕세자나 신하들이 출입하였다.</t>
+          <t>'광화'는 '군주에 의한 덕화(德化)'라는 뜻이다. 임금이 덕으로 사람들의 마음을 좋은 쪽으로 바꾼다는 말이다.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 원문 바탕</t>
+          <t>📜 앞 문장 국가유산청 원문 / 뒷 문장은 표준국어대사전 덕화·감화를 이어 푼 것</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>M2-a</t>
+          <t>M1-c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>문 앞 · 홍례문 알림창</t>
+          <t>문 앞 · 광화문 알림창</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>홍례문(弘禮門)</t>
+          <t>광화문은 경복궁의 정문으로 3개의 홍예문으로 이루어져 있는데, 중앙의 홍예문은 왕이 드나들었고 좌우의 홍예문은 왕세자나 신하들이 출입하였다.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>📜 1446년의 이름 · 2026-09-22 흥례문(興禮門)에서 바꿈</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 원문 바탕</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>M2-b</t>
+          <t>M2-a</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2025,24 +2037,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>지금은 흥례문(興禮門)이라 부른다. 고종 때 경복궁을 다시 지으면서, 청나라 건륭제의 이름인 홍력(弘曆)의 글자를 피하려고 이름을 바꾸었다.</t>
+          <t>홍례문(弘禮門)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>📜 국가유산청 「궁궐의 현판과 주련」 · 📝 초안 → 🙋 "응 고치자." (2026-09-22)</t>
+          <t>📜 1446년의 이름 · 2026-09-22 흥례문(興禮門)에서 바꿈</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>M2-c</t>
+          <t>M2-b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2052,51 +2064,51 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>홍례문은 광화문과 근정문 사이에 있는 경복궁의 중문이다. 이 문 안뜰에서 신하들이 임금을 뵙는 조회가 열렸고, 임금의 명을 널리 알리는 일도 이곳에서 이루어졌다.</t>
+          <t>지금은 흥례문(興禮門)이라 부른다. 고종 때 경복궁을 다시 지으면서, 청나라 건륭제의 이름인 홍력(弘曆)의 글자를 피하려고 이름을 바꾸었다.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>📜 국가유산청 / 📝 「조회」·「교서 반포」는 풀어 씀</t>
+          <t>📜 국가유산청 「궁궐의 현판과 주련」 · 📝 초안 → 🙋 "응 고치자." (2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>M3-a</t>
+          <t>M2-c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>문 앞 · 영제교 알림창</t>
+          <t>문 앞 · 홍례문 알림창</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>영제교(永濟橋)</t>
+          <t>홍례문은 광화문과 근정문 사이에 있는 경복궁의 중문이다. 이 문 안뜰에서 신하들이 임금을 뵙는 조회가 열렸고, 임금의 명을 널리 알리는 일도 이곳에서 이루어졌다.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>📜 국가유산청 / 📝 「조회」·「교서 반포」는 풀어 씀</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>M3-b</t>
+          <t>M3-a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2106,24 +2118,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>이 돌다리에 영제교라는 이름이 붙은 것은 세종 8년(1426)이다.</t>
+          <t>영제교(永濟橋)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>📜 국가유산청 「궁 안팎을 가르는 경계, 금천교」 · 🔴 永濟의 뜻풀이는 기관 원문에 없어 넣지 않음</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>M3-c</t>
+          <t>M3-b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2133,51 +2145,51 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>영제교는 궁궐의 안과 밖을 가르는 경계였다. 이 다리를 넘어가면 궐을 나간 것으로 쳤다. 임금이 왕실 어른이나 사신을 맞이하고 배웅할 때도 이 다리까지 나왔다.</t>
+          <t>이 돌다리에 영제교라는 이름이 붙은 것은 세종 8년(1426)이다.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>📜 국가유산청 / 📝 「금천교」를 「영제교」로 통일</t>
+          <t>📜 국가유산청 「궁 안팎을 가르는 경계, 금천교」 · 🔴 永濟의 뜻풀이는 기관 원문에 없어 넣지 않음</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>M4-a</t>
+          <t>M3-c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>문 앞 · 근정문 알림창</t>
+          <t>문 앞 · 영제교 알림창</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>근정문(勤政門)</t>
+          <t>영제교는 궁궐의 안과 밖을 가르는 경계였다. 이 다리를 넘어가면 궐을 나간 것으로 쳤다. 임금이 왕실 어른이나 사신을 맞이하고 배웅할 때도 이 다리까지 나왔다.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>📜 국가유산청 / 📝 「금천교」를 「영제교」로 통일</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M4-b</t>
+          <t>M4-a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2187,24 +2199,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>'근정'은 '천하의 일을 부지런히 하여 잘 다스리다'는 뜻이다. 이 문 안에 있는 근정전과 같은 이름을 쓴다.</t>
+          <t>근정문(勤政門)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>📜 국가유산청 · 근정전 알림창은 뜻을 되풀이하지 않으므로 겹치지 않는다(2026-09-21 닫힘)</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>M4-c</t>
+          <t>M4-b</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2214,51 +2226,51 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>근정문은 근정전으로 들어가는 정문으로, 궁궐 정전의 정문 가운데 유일하게 2층으로 지었다. 임금이 세상을 떠난 뒤 다음 임금이 이 문에서 즉위식을 치르기도 했다. 단종과 성종, 명종이 이곳에서 왕위에 올랐다.</t>
+          <t>'근정'은 '천하의 일을 부지런히 하여 잘 다스리다'는 뜻이다. 이 문 안에 있는 근정전과 같은 이름을 쓴다.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>🙋 마지막 문장 사용자 / 📜 국가유산청 / 📝 「국장이 있을 때」를 풀어 씀</t>
+          <t>📜 국가유산청 · 근정전 알림창은 뜻을 되풀이하지 않으므로 겹치지 않는다(2026-09-21 닫힘)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>M6-a</t>
+          <t>M4-c</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>문 앞 · 사정문 알림창</t>
+          <t>문 앞 · 근정문 알림창</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>사정문(思政門)</t>
+          <t>근정문은 근정전으로 들어가는 정문으로, 궁궐 정전의 정문 가운데 유일하게 2층으로 지었다. 임금이 세상을 떠난 뒤 다음 임금이 이 문에서 즉위식을 치르기도 했다. 단종과 성종, 명종이 이곳에서 왕위에 올랐다.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>🙋 마지막 문장 사용자 / 📜 국가유산청 / 📝 「국장이 있을 때」를 풀어 씀</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>M6-b</t>
+          <t>M6-a</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2268,24 +2280,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>사정은 백성을 바르게 다스릴 일을 생각한다는 뜻으로 정도전이 지었다.</t>
+          <t>사정문(思政門)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 「정도전이 작명하였다」</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>M6-c</t>
+          <t>M6-b</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2295,51 +2307,51 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>사정문은 사정전 남쪽에 있는 문으로 사정전은 왕이 신하들과 함께 일상 업무를 보던 집무실이었다. 이곳에서 매일 아침 업무 보고와 회의, 경연 등이 이루어졌다.</t>
+          <t>사정은 백성을 바르게 다스릴 일을 생각한다는 뜻으로 정도전이 지었다.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 / ✅ 「왕은」→「왕이」 사용자 승인 (2026-09-21)</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 「정도전이 작명하였다」</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>M5-a</t>
+          <t>M6-c</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>문 앞 · 근정전 알림창</t>
+          <t>문 앞 · 사정문 알림창</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>근정전(勤政殿)</t>
+          <t>사정문은 사정전 남쪽에 있는 문으로 사정전은 왕이 신하들과 함께 일상 업무를 보던 집무실이었다. 이곳에서 매일 아침 업무 보고와 회의, 경연 등이 이루어졌다.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 / ✅ 「왕은」→「왕이」 사용자 승인 (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>M5-b</t>
+          <t>M5-a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2349,78 +2361,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>근정전은 근정문 안에 있는 경복궁의 정전이다. 즉위식과 하례, 사신을 맞이하는 일과 궁중 잔치가 이곳에서 열렸다.</t>
+          <t>근정전(勤政殿)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>📜 국가유산청 · 뜻풀이는 바로 앞 근정문에서 말하므로 넣지 않음</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>M5-b</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>문 앞 · 근정전 알림창</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>근정전은 근정문 안에 있는 경복궁의 정전이다. 즉위식과 하례, 사신을 맞이하는 일과 궁중 잔치가 이곳에서 열렸다.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>📜 국가유산청 · 뜻풀이는 바로 앞 근정문에서 말하므로 넣지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>M5-c</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>문 앞 · 근정전 알림창</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>역할 2</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>정종과 세종, 세조, 중종, 선조가 이곳에서 왕위에 올랐다. 앞마당 가운데에는 삼도(三道)라는 세 줄기 길이 있고, 양옆에는 정1품부터 정9품까지 신하들이 서던 품계석이 놓여 있다.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>📜 국가유산청 원문 두 대목</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>U-01</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>지도 · 육조거리 튜토리얼</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>조작키 바로 위 가운데 한 줄 — 1단계(▲만 켜짐)</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>▲를 누르면 앞으로 이동합니다.</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ▲는 발화에서 빠져 있어 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>U-02</t>
+          <t>U-01</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2430,24 +2442,24 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄 — 2단계(◀만 켜짐)</t>
+          <t>조작키 바로 위 가운데 한 줄 — 1단계(▲만 켜짐)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>◀를 눌러 왼쪽 대문 앞으로 이동하세요.</t>
+          <t>▲를 누르면 앞으로 이동합니다.</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ◀는 내가 넣음 → 🙋 "맞아")</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ▲는 발화에서 빠져 있어 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>U-03</t>
+          <t>U-02</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2457,132 +2469,132 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄 — 연습 판이 걷힌 뒤(▲◀▶ 모두)</t>
+          <t>조작키 바로 위 가운데 한 줄 — 2단계(◀만 켜짐)</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>이제 광화문 앞으로 이동하세요.</t>
+          <t>◀를 눌러 왼쪽 대문 앞으로 이동하세요.</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ◀는 내가 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>U-04</t>
+          <t>U-03</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>연습 판 · 점검 퀴즈 자리</t>
+          <t>지도 · 육조거리 튜토리얼</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>설명 글(위) — 아래 태블릿 그림(왼쪽)·포스터 그림(오른쪽)·닫기 B-08</t>
+          <t>조작키 바로 위 가운데 한 줄 — 연습 판이 걷힌 뒤(▲◀▶ 모두)</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>광화문부터는 단어를 완성한 뒤, 퀴즈를 풀어야 합니다. 포스터에서 정답을 찾아서 세 자리 숫자를 입력하세요.</t>
+          <t>이제 광화문 앞으로 이동하세요.</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장 · 낙관 없이 판이 걷힌다</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>U-05</t>
+          <t>U-04</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>지도 · 육조거리 튜토리얼</t>
+          <t>연습 판 · 점검 퀴즈 자리</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 실마리를 누르고 지도로 돌아왔을 때</t>
+          <t>설명 글(위) — 아래 태블릿 그림(왼쪽)·포스터 그림(오른쪽)·닫기 B-08</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 관청의 대문 중 하나에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>광화문부터는 단어를 완성한 뒤, 퀴즈를 풀어야 합니다. 포스터에서 정답을 찾아서 세 자리 숫자를 입력하세요.</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장 · 실마리는 오른쪽 위 관청 대문 한 곳에서만</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장 · 낙관 없이 판이 걷힌다</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>U-06</t>
+          <t>U-05</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>지도 · 실마리 곳(튜토리얼 · 본편)</t>
+          <t>지도 · 육조거리 튜토리얼</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈)</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 실마리를 누르고 지도로 돌아왔을 때</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>이 문제를 맞히면 실마리가 하나 풀릴 것이오!</t>
+          <t>오른쪽 관청의 대문 중 하나에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장의 「풀면」→「맞히면」 → 🙋 "좋아" · 튜토리얼에서 확정 · 본편 곳 19개(U-12~U-30)에서도 같은 글 — 🙋 2026-09-25 "응 좋아." (담장·개울가는 말하는 이가 없어도 됨 · 튜토리얼 관청 대문과 같다)</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장 · 실마리는 오른쪽 위 관청 대문 한 곳에서만</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>U-07</t>
+          <t>U-06</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>지도 · 근정전 앞마당</t>
+          <t>지도 · 실마리 곳(튜토리얼 · 본편)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 근정전 알림창(M5)을 닫은 뒤</t>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈)</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>아직 쓰지 않은 실마리가 있습니다. 품계석 앞 관리들에게 차례로 다가가 남은 실마리 문제를 모두 풀면 사정문으로 갈 수 있습니다.</t>
+          <t>이 문제를 맞히면 실마리가 하나 풀릴 것이오!</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장의 「풀면」→「맞히면」 → 🙋 "좋아" · 튜토리얼에서 확정 · 본편 곳 19개(U-12~U-30)에서도 같은 글 — 🙋 2026-09-25 "응 좋아." (담장·개울가는 말하는 이가 없어도 됨 · 튜토리얼 관청 대문과 같다)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2592,24 +2604,24 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 처음과 한 관리를 마칠 때마다</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 근정전 알림창(M5)을 닫은 뒤</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>이제 {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+          <t>아직 쓰지 않은 실마리가 있습니다. 품계석 앞 관리들에게 차례로 다가가 남은 실마리 문제를 모두 풀면 사정문으로 갈 수 있습니다.</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}=왼쪽/오른쪽 · {n}=첫/두/세/네 — 코드가 바꿔 넣는다(예: 이제 왼쪽 줄 첫 번째 관리에게 가 보세요.) · 첫 번째 = 들어선 쪽(아래)에서 가장 가까운 관리</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>U-09</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2619,24 +2631,24 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈) — 관리에게 닿았을 때</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 처음과 한 관리를 마칠 때마다</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>남겨 둔 실마리가 있구려. 이 문제를 맞혀 보시오!</t>
+          <t>이제 {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}=왼쪽/오른쪽 · {n}=첫/두/세/네 — 코드가 바꿔 넣는다(예: 이제 왼쪽 줄 첫 번째 관리에게 가 보세요.) · 첫 번째 = 들어선 쪽(아래)에서 가장 가까운 관리</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>U-09</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2646,24 +2658,24 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 다 풀기 전에 사정문 쪽 길목에 닿아 막혔을 때</t>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈) — 관리에게 닿았을 때</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>아직 풀지 않은 실마리 문제가 남아 있습니다. {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+          <t>남겨 둔 실마리가 있구려. 이 문제를 맞혀 보시오!</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}·{n}은 U-08과 같다(예: 오른쪽 줄 두 번째)</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2673,51 +2685,51 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄(U-03 자리) — 마지막 문제를 맞혀 낙관(L-01)이 찍힌 뒤</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 다 풀기 전에 사정문 쪽 길목에 닿아 막혔을 때</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>모든 실마리를 풀었습니다. 이제 사정문으로 이동하세요.</t>
+          <t>아직 풀지 않은 실마리 문제가 남아 있습니다. {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}·{n}은 U-08과 같다(예: 오른쪽 줄 두 번째)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>U-12</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>지도 · 광화문 실마리 곳</t>
+          <t>지도 · 근정전 앞마당</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>조작키 바로 위 가운데 한 줄(U-03 자리) — 마지막 문제를 맞혀 낙관(L-01)이 찍힌 뒤</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 분홍 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>모든 실마리를 풀었습니다. 이제 사정문으로 이동하세요.</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>U-13</t>
+          <t>U-12</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2727,12 +2739,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 지팡이를 든 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 분홍 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2744,7 +2756,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>U-14</t>
+          <t>U-13</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2754,12 +2766,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 파란 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 지팡이를 든 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2771,22 +2783,22 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>U-15</t>
+          <t>U-14</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>지도 · 홍례문 실마리 곳</t>
+          <t>지도 · 광화문 실마리 곳</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 파란 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2798,7 +2810,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>U-16</t>
+          <t>U-15</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2808,12 +2820,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 남색 치마를 입은 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -2825,7 +2837,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>U-17</t>
+          <t>U-16</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2835,12 +2847,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 남색 치마를 입은 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2852,22 +2864,22 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>U-18</t>
+          <t>U-17</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>지도 · 영제교 실마리 곳</t>
+          <t>지도 · 홍례문 실마리 곳</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2879,7 +2891,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>U-19</t>
+          <t>U-18</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2889,12 +2901,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2906,7 +2918,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>U-20</t>
+          <t>U-19</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2916,12 +2928,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -2933,7 +2945,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>U-21</t>
+          <t>U-20</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2943,12 +2955,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 개울가에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2960,22 +2972,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>U-22</t>
+          <t>U-21</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>지도 · 근정문 실마리 곳</t>
+          <t>지도 · 영제교 실마리 곳</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 개울가에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -2987,7 +2999,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>U-23</t>
+          <t>U-22</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2997,12 +3009,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3014,7 +3026,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>U-24</t>
+          <t>U-23</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3024,12 +3036,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 파란 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3041,7 +3053,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>U-25</t>
+          <t>U-24</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3051,12 +3063,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 파란 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3068,7 +3080,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>U-26</t>
+          <t>U-25</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3078,12 +3090,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 5번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 5</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3095,22 +3107,22 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>U-27</t>
+          <t>U-26</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>지도 · 사정문 실마리 곳</t>
+          <t>지도 · 근정문 실마리 곳</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 5번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 5</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 남색 치마를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3122,7 +3134,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>U-28</t>
+          <t>U-27</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3132,12 +3144,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 남색 치마를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3149,7 +3161,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>U-29</t>
+          <t>U-28</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3159,12 +3171,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3176,25 +3188,52 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
+          <t>U-29</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
           <t>U-30</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>지도 · 사정문 실마리 곳</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>왼쪽 노란 저고리를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
         </is>

--- a/content/ui_text.xlsx
+++ b/content/ui_text.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1252,30 +1252,34 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Q-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>문 앞 · 자모 조합 판</t>
+          <t>지도 화면 · 문 앞 화면</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>할 일 안내</t>
+          <t>점수 칸 — 화면 왼쪽 위(오른쪽 위 미니맵과 짝 · 같은 한지 상자) · 판·알림창이 떠도 보인다 · {n}에 지금 점수(시작은 0)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>자음과 모음을 조합해 빈칸에 들어갈 단어를 완성하세요.</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+          <t>{n}점</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>🙋 "응 좋아." (2026-09-28 · 2-6 · 이름표·만점 없음) · 오를 때 칸 옆에 +{n}(숫자라 코드가 적는다)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Q-02</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1285,12 +1289,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>넣는 법 안내</t>
+          <t>할 일 안내</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>손가락으로 끌어다 놓거나 자판으로 입력할 수 있어요.</t>
+          <t>자음과 모음을 조합해 빈칸에 들어갈 단어를 완성하세요.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
@@ -1298,7 +1302,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1308,51 +1312,47 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>실마리 버튼</t>
+          <t>넣는 법 안내</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>실마리</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>남은 수는 적지 않는다</t>
-        </is>
-      </c>
+          <t>손가락으로 끌어다 놓거나 자판으로 입력할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Q-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>문 앞 · 힌트 퀴즈 판</t>
+          <t>문 앞 · 자모 조합 판</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>머리 안내</t>
+          <t>실마리 버튼</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>정답을 맞히면 자음 혹은 모음 하나가 공개됩니다.</t>
+          <t>실마리</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>판 맨 위. 2026-09-19 확정 · 같은 날 「자음이나」→「자음 혹은」</t>
+          <t>남은 수는 적지 않는다</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>B-06</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1362,51 +1362,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>돌아가기 버튼</t>
+          <t>머리 안내</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>돌아가기</t>
+          <t>정답을 맞히면 자음 혹은 모음 하나가 공개됩니다.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>풀지 않고 자모 조합 판으로 돌아간다. 실마리는 줄지 않는다</t>
+          <t>판 맨 위. 2026-09-19 확정 · 같은 날 「자음이나」→「자음 혹은」</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Q-04</t>
+          <t>B-06</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>문 앞 · 점검 퀴즈 판</t>
+          <t>문 앞 · 힌트 퀴즈 판</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>머리 안내</t>
+          <t>돌아가기 버튼</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>포스터에서 답을 찾아 세 자리 숫자를 입력하세요.</t>
+          <t>돌아가기</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>판 맨 위. 2026-09-19 확정 · 2026-09-26 「옆에 적힌」 뺌(사용자)</t>
+          <t>풀지 않고 자모 조합 판으로 돌아간다. 실마리는 줄지 않는다</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>B-07</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1416,24 +1416,24 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>확인 버튼</t>
+          <t>머리 안내</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>포스터에서 답을 찾아 세 자리 숫자를 입력하세요.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>입력칸 바로 옆. 누르면 판정(Enter도 같게). 2026-09-19 확정</t>
+          <t>판 맨 위. 2026-09-19 확정 · 2026-09-26 「옆에 적힌」 뺌(사용자)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Q-05</t>
+          <t>B-07</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1443,24 +1443,24 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>없는 숫자일 때</t>
+          <t>확인 버튼</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>포스터에 없는 숫자입니다.</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>해설 자리에 뜬다(흔들린 뒤). 두 학년 공용. 2026-09-19 확정</t>
+          <t>입력칸 바로 옆. 누르면 판정(Enter도 같게). 2026-09-19 확정</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>Q-05</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1470,105 +1470,105 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>같은 학년의 다른 문항 코드일 때</t>
+          <t>없는 숫자일 때</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>문제를 다시 확인하세요.</t>
+          <t>포스터에 없는 숫자입니다.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>해설 자리에 뜬다(흔들린 뒤). 그 코드가 다른 문항의 정답이든 오답이든 같다. 두 학년 공용. 2026-09-19 확정</t>
+          <t>해설 자리에 뜬다(흔들린 뒤). 두 학년 공용. 2026-09-19 확정</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>근정전 앞마당 · 힌트 퀴즈 판</t>
+          <t>문 앞 · 점검 퀴즈 판</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>판 맨 위 머리 안내(Q-03 자리 · 근정전에서만 Q-03 대신)</t>
+          <t>같은 학년의 다른 문항 코드일 때</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>앞에서 풀지 않은 실마리 문제입니다. 모두 맞히면 사정문으로 갈 수 있습니다.</t>
+          <t>문제를 다시 확인하세요.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 📝 초안 → 🙋 "초안으로 할게 대신 줄바꿈해줘." — 화면에서 문장마다 한 줄(두 줄). 근정전 문제는 맞혀도 자모가 채워지지 않아 Q-03이 맞지 않는다(🙋 "근정전 앞마당에서 힌트를 풀 때는 정답을 맞히면 자음 혹은 모음 하나가 공개됩니다. 라는 지시문을 바꿔야 할 것 같아.")</t>
+          <t>해설 자리에 뜬다(흔들린 뒤). 그 코드가 다른 문항의 정답이든 오답이든 같다. 두 학년 공용. 2026-09-19 확정</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>문 앞 · 퀴즈</t>
+          <t>근정전 앞마당 · 힌트 퀴즈 판</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>정답 낙관의 글</t>
+          <t>판 맨 위 머리 안내(Q-03 자리 · 근정전에서만 Q-03 대신)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>앞에서 풀지 않은 실마리 문제입니다. 모두 맞히면 사정문으로 갈 수 있습니다.</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>점검 퀴즈를 맞히면 판 한가운데 크게 찍힌다. 2026-09-19 확정</t>
+          <t>2026-09-26 📝 초안 → 🙋 "초안으로 할게 대신 줄바꿈해줘." — 화면에서 문장마다 한 줄(두 줄). 근정전 문제는 맞혀도 자모가 채워지지 않아 Q-03이 맞지 않는다(🙋 "근정전 앞마당에서 힌트를 풀 때는 정답을 맞히면 자음 혹은 모음 하나가 공개됩니다. 라는 지시문을 바꿔야 할 것 같아.")</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>사정전 · 알현</t>
+          <t>문 앞 · 퀴즈</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>세종의 첫 말 (자막)</t>
+          <t>정답 낙관의 글</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>어서 오너라.</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21) · 화면 차례는 S-08 → S-07 → S-09</t>
+          <t>점검 퀴즈를 맞히면 판 한가운데 크게 찍힌다. 2026-09-19 확정</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>S-07</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>플레이어의 말</t>
+          <t>세종의 첫 말 (자막)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>한글을 만들어주셔서 감사합니다.</t>
+          <t>어서 오너라.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21 「창제해 주셔서」에서 바뀜)</t>
+          <t>🙋 사용자 문장 (2026-09-21) · 화면 차례는 S-08 → S-07 → S-09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1605,78 +1605,78 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>세종의 마지막 말 (자막)</t>
+          <t>플레이어의 말</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>한글을 많이 아껴 다오.</t>
+          <t>한글을 만들어주셔서 감사합니다.</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 (2026-09-21) · 이 말 뒤 게임이 끝난다</t>
+          <t>🙋 사용자 문장 (2026-09-21 「창제해 주셔서」에서 바뀜)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>N-01</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>끝 · 갈무리 판</t>
+          <t>사정전 · 알현</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>판 타이틀</t>
+          <t>세종의 마지막 말 (자막)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>갈무리</t>
+          <t>한글을 많이 아껴 다오.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>📝 내 안 · 🙋 승인 (2026-09-21) · 표준국어대사전 「물건 따위를 잘 정리하거나 간수함」 · 문장 11장에만 붙는다(서약서 판에는 없다)</t>
+          <t>🙋 사용자 문장 (2026-09-21) · 이 말 뒤 게임이 끝난다</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>N-01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>끝 · 서약서 판</t>
+          <t>끝 · 갈무리 판</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>판 타이틀</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>서약서</t>
+          <t>갈무리</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 🙋 승인 (2026-09-21) · 띄어 보이는 것은 글자 간격(디자인)</t>
+          <t>📝 내 안 · 🙋 승인 (2026-09-21) · 표준국어대사전 「물건 따위를 잘 정리하거나 간수함」 · 문장 11장에만 붙는다(서약서 판에는 없다)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>요지</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>나는 세종대왕께서 만드신 한글을 아끼고 아름답게 사용하겠습니다.</t>
+          <t>서약서</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 뜻은 🙋 사용자 「한글을 아끼고 아름답게 사용하겠다」 · 승인</t>
+          <t>📝 내 초안 · 🙋 승인 (2026-09-21) · 띄어 보이는 것은 글자 간격(디자인)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>O-02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>조항 1</t>
+          <t>요지</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>하나, 맞춤법을 지키며 바르게 쓰겠습니다.</t>
+          <t>나는 세종대왕께서 만드신 한글을 아끼고 아름답게 사용하겠습니다.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장</t>
+          <t>📝 내 초안 · 뜻은 🙋 사용자 「한글을 아끼고 아름답게 사용하겠다」 · 승인</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,24 +1740,24 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>조항 2</t>
+          <t>조항 1</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>하나, 남을 아프게 하는 말 대신 고운 말을 쓰겠습니다.</t>
+          <t>하나, 맞춤법을 지키며 바르게 쓰겠습니다.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안 · 🙋 "이건 좋아."</t>
+          <t>🙋 사용자 문장</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-04</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1767,24 +1767,24 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>조항 3</t>
+          <t>조항 2</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>하나, 한글이 만들어진 뜻을 기억하며 소중히 여기겠습니다.</t>
+          <t>하나, 남을 아프게 하는 말 대신 고운 말을 쓰겠습니다.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>📝 내 초안(넷째 안) · 🙋 "응 지금 걸로 하자."</t>
+          <t>📝 내 초안 · 🙋 "이건 좋아."</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1794,24 +1794,24 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>체크 칸 글</t>
+          <t>조항 3</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>위와 같이 서약합니다.</t>
+          <t>하나, 한글이 만들어진 뜻을 기억하며 소중히 여기겠습니다.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>🙋 "위와 같이 서약합니다. 좋아." · 체크하면 게임이 끝난다</t>
+          <t>📝 내 초안(넷째 안) · 🙋 "응 지금 걸로 하자."</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1821,24 +1821,24 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>체크 칸 글</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>(플레이한 날짜)</t>
+          <t>위와 같이 서약합니다.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>🙋 "날짜가 플레이하는 날로 나타나는 것도 좋아." · 🛠 기기 날짜로 채운다 · 서약서 판이 뜨는 날을 찍는다(🙋 "그렇게 해." 2026-09-22) · 꼴은 「2026년 9월 21일」(🙋 "지금 상태가 좋아." 2026-09-22)</t>
+          <t>🙋 "위와 같이 서약합니다. 좋아." · 체크하면 게임이 끝난다</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>B-09</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1848,24 +1848,24 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>저장 버튼</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(플레이한 날짜)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 왼쪽 · 누르면 갈무리 11장 + 서약서를 PDF로 내려받는다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+          <t>🙋 "날짜가 플레이하는 날로 나타나는 것도 좋아." · 🛠 기기 날짜로 채운다 · 서약서 판이 뜨는 날을 찍는다(🙋 "그렇게 해." 2026-09-22) · 꼴은 「2026년 9월 21일」(🙋 "지금 상태가 좋아." 2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>B-10</t>
+          <t>B-09</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1875,105 +1875,105 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>종료 버튼</t>
+          <t>저장 버튼</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 오른쪽 · 누르면 책상에 엎드려 잠든 모습으로 간다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 왼쪽 · 누르면 갈무리 11장 + 서약서를 PDF로 내려받는다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>끝 · 서약서 판</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>종료 버튼</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>종료</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>서약서에 체크하면 나타난다 · 화면 아래 가운데 오른쪽 · 누르면 책상에 엎드려 잠든 모습으로 간다 · 🙋 "저장이 왼쪽 종료가 오른쪽" (2026-09-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>F-01</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>끝 · 저장</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>내려받는 PDF 파일 이름</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>세종대왕을 알현하라!</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>뒤에 .pdf를 붙인다 · 🙋 "그냥 세종대왕을 알현하라! 이걸로 하자." (2026-09-22) · T-01과 같은 글</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>B-08</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>문 앞 · 알림창</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>닫기 버튼</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>닫기</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-09-21 🙋 "닫기로 해."</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>M1-a</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>문 앞 · 광화문 알림창</t>
+          <t>문 앞 · 알림창</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>닫기 버튼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>광화문(光化門)</t>
+          <t>닫기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>2026-09-21 🙋 "닫기로 해."</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>M1-b</t>
+          <t>M1-a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1983,24 +1983,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>'광화'는 '군주에 의한 덕화(德化)'라는 뜻이다. 임금이 덕으로 사람들의 마음을 좋은 쪽으로 바꾼다는 말이다.</t>
+          <t>광화문(光化門)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>📜 앞 문장 국가유산청 원문 / 뒷 문장은 표준국어대사전 덕화·감화를 이어 푼 것</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>M1-c</t>
+          <t>M1-b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2010,51 +2010,51 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>광화문은 경복궁의 정문으로 3개의 홍예문으로 이루어져 있는데, 중앙의 홍예문은 왕이 드나들었고 좌우의 홍예문은 왕세자나 신하들이 출입하였다.</t>
+          <t>'광화'는 '군주에 의한 덕화(德化)'라는 뜻이다. 임금이 덕으로 사람들의 마음을 좋은 쪽으로 바꾼다는 말이다.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 원문 바탕</t>
+          <t>📜 앞 문장 국가유산청 원문 / 뒷 문장은 표준국어대사전 덕화·감화를 이어 푼 것</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>M2-a</t>
+          <t>M1-c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>문 앞 · 홍례문 알림창</t>
+          <t>문 앞 · 광화문 알림창</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>홍례문(弘禮門)</t>
+          <t>광화문은 경복궁의 정문으로 3개의 홍예문으로 이루어져 있는데, 중앙의 홍예문은 왕이 드나들었고 좌우의 홍예문은 왕세자나 신하들이 출입하였다.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>📜 1446년의 이름 · 2026-09-22 흥례문(興禮門)에서 바꿈</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 원문 바탕</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>M2-b</t>
+          <t>M2-a</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2064,24 +2064,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>지금은 흥례문(興禮門)이라 부른다. 고종 때 경복궁을 다시 지으면서, 청나라 건륭제의 이름인 홍력(弘曆)의 글자를 피하려고 이름을 바꾸었다.</t>
+          <t>홍례문(弘禮門)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>📜 국가유산청 「궁궐의 현판과 주련」 · 📝 초안 → 🙋 "응 고치자." (2026-09-22)</t>
+          <t>📜 1446년의 이름 · 2026-09-22 흥례문(興禮門)에서 바꿈</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>M2-c</t>
+          <t>M2-b</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2091,51 +2091,51 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>홍례문은 광화문과 근정문 사이에 있는 경복궁의 중문이다. 이 문 안뜰에서 신하들이 임금을 뵙는 조회가 열렸고, 임금의 명을 널리 알리는 일도 이곳에서 이루어졌다.</t>
+          <t>지금은 흥례문(興禮門)이라 부른다. 고종 때 경복궁을 다시 지으면서, 청나라 건륭제의 이름인 홍력(弘曆)의 글자를 피하려고 이름을 바꾸었다.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>📜 국가유산청 / 📝 「조회」·「교서 반포」는 풀어 씀</t>
+          <t>📜 국가유산청 「궁궐의 현판과 주련」 · 📝 초안 → 🙋 "응 고치자." (2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>M3-a</t>
+          <t>M2-c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>문 앞 · 영제교 알림창</t>
+          <t>문 앞 · 홍례문 알림창</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>영제교(永濟橋)</t>
+          <t>홍례문은 광화문과 근정문 사이에 있는 경복궁의 중문이다. 이 문 안뜰에서 신하들이 임금을 뵙는 조회가 열렸고, 임금의 명을 널리 알리는 일도 이곳에서 이루어졌다.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>📜 국가유산청 / 📝 「조회」·「교서 반포」는 풀어 씀</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>M3-b</t>
+          <t>M3-a</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2145,24 +2145,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>이 돌다리에 영제교라는 이름이 붙은 것은 세종 8년(1426)이다.</t>
+          <t>영제교(永濟橋)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>📜 국가유산청 「궁 안팎을 가르는 경계, 금천교」 · 🔴 永濟의 뜻풀이는 기관 원문에 없어 넣지 않음</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>M3-c</t>
+          <t>M3-b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2172,51 +2172,51 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>영제교는 궁궐의 안과 밖을 가르는 경계였다. 이 다리를 넘어가면 궐을 나간 것으로 쳤다. 임금이 왕실 어른이나 사신을 맞이하고 배웅할 때도 이 다리까지 나왔다.</t>
+          <t>이 돌다리에 영제교라는 이름이 붙은 것은 세종 8년(1426)이다.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>📜 국가유산청 / 📝 「금천교」를 「영제교」로 통일</t>
+          <t>📜 국가유산청 「궁 안팎을 가르는 경계, 금천교」 · 🔴 永濟의 뜻풀이는 기관 원문에 없어 넣지 않음</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M4-a</t>
+          <t>M3-c</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>문 앞 · 근정문 알림창</t>
+          <t>문 앞 · 영제교 알림창</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>근정문(勤政門)</t>
+          <t>영제교는 궁궐의 안과 밖을 가르는 경계였다. 이 다리를 넘어가면 궐을 나간 것으로 쳤다. 임금이 왕실 어른이나 사신을 맞이하고 배웅할 때도 이 다리까지 나왔다.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>📜 국가유산청 / 📝 「금천교」를 「영제교」로 통일</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>M4-b</t>
+          <t>M4-a</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2226,24 +2226,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>'근정'은 '천하의 일을 부지런히 하여 잘 다스리다'는 뜻이다. 이 문 안에 있는 근정전과 같은 이름을 쓴다.</t>
+          <t>근정문(勤政門)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>📜 국가유산청 · 근정전 알림창은 뜻을 되풀이하지 않으므로 겹치지 않는다(2026-09-21 닫힘)</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>M4-c</t>
+          <t>M4-b</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2253,51 +2253,51 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>근정문은 근정전으로 들어가는 정문으로, 궁궐 정전의 정문 가운데 유일하게 2층으로 지었다. 임금이 세상을 떠난 뒤 다음 임금이 이 문에서 즉위식을 치르기도 했다. 단종과 성종, 명종이 이곳에서 왕위에 올랐다.</t>
+          <t>'근정'은 '천하의 일을 부지런히 하여 잘 다스리다'는 뜻이다. 이 문 안에 있는 근정전과 같은 이름을 쓴다.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>🙋 마지막 문장 사용자 / 📜 국가유산청 / 📝 「국장이 있을 때」를 풀어 씀</t>
+          <t>📜 국가유산청 · 근정전 알림창은 뜻을 되풀이하지 않으므로 겹치지 않는다(2026-09-21 닫힘)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>M6-a</t>
+          <t>M4-c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>문 앞 · 사정문 알림창</t>
+          <t>문 앞 · 근정문 알림창</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>사정문(思政門)</t>
+          <t>근정문은 근정전으로 들어가는 정문으로, 궁궐 정전의 정문 가운데 유일하게 2층으로 지었다. 임금이 세상을 떠난 뒤 다음 임금이 이 문에서 즉위식을 치르기도 했다. 단종과 성종, 명종이 이곳에서 왕위에 올랐다.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>🙋 마지막 문장 사용자 / 📜 국가유산청 / 📝 「국장이 있을 때」를 풀어 씀</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>M6-b</t>
+          <t>M6-a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2307,24 +2307,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>이름 이야기</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>사정은 백성을 바르게 다스릴 일을 생각한다는 뜻으로 정도전이 지었다.</t>
+          <t>사정문(思政門)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 「정도전이 작명하였다」</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>M6-c</t>
+          <t>M6-b</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2334,51 +2334,51 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름 이야기</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>사정문은 사정전 남쪽에 있는 문으로 사정전은 왕이 신하들과 함께 일상 업무를 보던 집무실이었다. 이곳에서 매일 아침 업무 보고와 회의, 경연 등이 이루어졌다.</t>
+          <t>사정은 백성을 바르게 다스릴 일을 생각한다는 뜻으로 정도전이 지었다.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>🙋 사용자 문장 / 📜 국가유산청 / ✅ 「왕은」→「왕이」 사용자 승인 (2026-09-21)</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 「정도전이 작명하였다」</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>M5-a</t>
+          <t>M6-c</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>문 앞 · 근정전 알림창</t>
+          <t>문 앞 · 사정문 알림창</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>근정전(勤政殿)</t>
+          <t>사정문은 사정전 남쪽에 있는 문으로 사정전은 왕이 신하들과 함께 일상 업무를 보던 집무실이었다. 이곳에서 매일 아침 업무 보고와 회의, 경연 등이 이루어졌다.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>📜 실제 이름</t>
+          <t>🙋 사용자 문장 / 📜 국가유산청 / ✅ 「왕은」→「왕이」 사용자 승인 (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>M5-b</t>
+          <t>M5-a</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2388,78 +2388,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>근정전은 근정문 안에 있는 경복궁의 정전이다. 즉위식과 하례, 사신을 맞이하는 일과 궁중 잔치가 이곳에서 열렸다.</t>
+          <t>근정전(勤政殿)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>📜 국가유산청 · 뜻풀이는 바로 앞 근정문에서 말하므로 넣지 않음</t>
+          <t>📜 실제 이름</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>M5-b</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>문 앞 · 근정전 알림창</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>근정전은 근정문 안에 있는 경복궁의 정전이다. 즉위식과 하례, 사신을 맞이하는 일과 궁중 잔치가 이곳에서 열렸다.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>📜 국가유산청 · 뜻풀이는 바로 앞 근정문에서 말하므로 넣지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>M5-c</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>문 앞 · 근정전 알림창</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>역할 2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>정종과 세종, 세조, 중종, 선조가 이곳에서 왕위에 올랐다. 앞마당 가운데에는 삼도(三道)라는 세 줄기 길이 있고, 양옆에는 정1품부터 정9품까지 신하들이 서던 품계석이 놓여 있다.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>📜 국가유산청 원문 두 대목</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>U-01</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>지도 · 육조거리 튜토리얼</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>조작키 바로 위 가운데 한 줄 — 1단계(▲만 켜짐)</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>▲를 누르면 앞으로 이동합니다.</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ▲는 발화에서 빠져 있어 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>U-02</t>
+          <t>U-01</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2469,24 +2469,24 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄 — 2단계(◀만 켜짐)</t>
+          <t>조작키 바로 위 가운데 한 줄 — 1단계(▲만 켜짐)</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>◀를 눌러 왼쪽 대문 앞으로 이동하세요.</t>
+          <t>▲를 누르면 앞으로 이동합니다.</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ◀는 내가 넣음 → 🙋 "맞아")</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ▲는 발화에서 빠져 있어 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>U-03</t>
+          <t>U-02</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2496,132 +2496,132 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄 — 연습 판이 걷힌 뒤(▲◀▶ 모두)</t>
+          <t>조작키 바로 위 가운데 한 줄 — 2단계(◀만 켜짐)</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>이제 광화문 앞으로 이동하세요.</t>
+          <t>◀를 눌러 왼쪽 대문 앞으로 이동하세요.</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장(기호 ◀는 내가 넣음 → 🙋 "맞아")</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>U-04</t>
+          <t>U-03</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>연습 판 · 점검 퀴즈 자리</t>
+          <t>지도 · 육조거리 튜토리얼</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>설명 글(위) — 아래 태블릿 그림(왼쪽)·포스터 그림(오른쪽)·닫기 B-08</t>
+          <t>조작키 바로 위 가운데 한 줄 — 연습 판이 걷힌 뒤(▲◀▶ 모두)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>광화문부터는 단어를 완성한 뒤, 퀴즈를 풀어야 합니다. 포스터에서 정답을 찾아서 세 자리 숫자를 입력하세요.</t>
+          <t>이제 광화문 앞으로 이동하세요.</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장 · 낙관 없이 판이 걷힌다</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>U-05</t>
+          <t>U-04</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>지도 · 육조거리 튜토리얼</t>
+          <t>연습 판 · 점검 퀴즈 자리</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 실마리를 누르고 지도로 돌아왔을 때</t>
+          <t>설명 글(위) — 아래 태블릿 그림(왼쪽)·포스터 그림(오른쪽)·닫기 B-08</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 관청의 대문 중 하나에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>광화문부터는 단어를 완성한 뒤, 퀴즈를 풀어야 합니다. 포스터에서 정답을 찾아서 세 자리 숫자를 입력하세요.</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장 · 실마리는 오른쪽 위 관청 대문 한 곳에서만</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1 · 사용자 문장 · 낙관 없이 판이 걷힌다</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>U-06</t>
+          <t>U-05</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>지도 · 실마리 곳(튜토리얼 · 본편)</t>
+          <t>지도 · 육조거리 튜토리얼</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈)</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 실마리를 누르고 지도로 돌아왔을 때</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>이 문제를 맞히면 실마리가 하나 풀릴 것이오!</t>
+          <t>오른쪽 관청의 대문 중 하나에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장의 「풀면」→「맞히면」 → 🙋 "좋아" · 튜토리얼에서 확정 · 본편 곳 19개(U-12~U-30)에서도 같은 글 — 🙋 2026-09-25 "응 좋아." (담장·개울가는 말하는 이가 없어도 됨 · 튜토리얼 관청 대문과 같다)</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장 · 실마리는 오른쪽 위 관청 대문 한 곳에서만</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>U-07</t>
+          <t>U-06</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>지도 · 근정전 앞마당</t>
+          <t>지도 · 실마리 곳(튜토리얼 · 본편)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 근정전 알림창(M5)을 닫은 뒤</t>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>아직 쓰지 않은 실마리가 있습니다. 품계석 앞 관리들에게 차례로 다가가 남은 실마리 문제를 모두 풀면 사정문으로 갈 수 있습니다.</t>
+          <t>이 문제를 맞히면 실마리가 하나 풀릴 것이오!</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 · HANDOFF 🟩 기1·기2 · 사용자 문장의 「풀면」→「맞히면」 → 🙋 "좋아" · 튜토리얼에서 확정 · 본편 곳 19개(U-12~U-30)에서도 같은 글 — 🙋 2026-09-25 "응 좋아." (담장·개울가는 말하는 이가 없어도 됨 · 튜토리얼 관청 대문과 같다)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>U-08</t>
+          <t>U-07</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 처음과 한 관리를 마칠 때마다</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 근정전 알림창(M5)을 닫은 뒤</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>이제 {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+          <t>아직 쓰지 않은 실마리가 있습니다. 품계석 앞 관리들에게 차례로 다가가 남은 실마리 문제를 모두 풀면 사정문으로 갈 수 있습니다.</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}=왼쪽/오른쪽 · {n}=첫/두/세/네 — 코드가 바꿔 넣는다(예: 이제 왼쪽 줄 첫 번째 관리에게 가 보세요.) · 첫 번째 = 들어선 쪽(아래)에서 가장 가까운 관리</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>U-09</t>
+          <t>U-08</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈) — 관리에게 닿았을 때</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 처음과 한 관리를 마칠 때마다</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>남겨 둔 실마리가 있구려. 이 문제를 맞혀 보시오!</t>
+          <t>이제 {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}=왼쪽/오른쪽 · {n}=첫/두/세/네 — 코드가 바꿔 넣는다(예: 이제 왼쪽 줄 첫 번째 관리에게 가 보세요.) · 첫 번째 = 들어선 쪽(아래)에서 가장 가까운 관리</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>U-09</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2685,24 +2685,24 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 다 풀기 전에 사정문 쪽 길목에 닿아 막혔을 때</t>
+          <t>자막 자리 한 줄(뒤 딤 · 화면을 누르면 힌트 퀴즈) — 관리에게 닿았을 때</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>아직 풀지 않은 실마리 문제가 남아 있습니다. {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
+          <t>남겨 둔 실마리가 있구려. 이 문제를 맞혀 보시오!</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}·{n}은 U-08과 같다(예: 오른쪽 줄 두 번째)</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>U-11</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2712,51 +2712,51 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>조작키 바로 위 가운데 한 줄(U-03 자리) — 마지막 문제를 맞혀 낙관(L-01)이 찍힌 뒤</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 다 풀기 전에 사정문 쪽 길목에 닿아 막혔을 때</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>모든 실마리를 풀었습니다. 이제 사정문으로 이동하세요.</t>
+          <t>아직 풀지 않은 실마리 문제가 남아 있습니다. {쪽} 줄 {n}번째 관리에게 가 보세요.</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다 · {쪽}·{n}은 U-08과 같다(예: 오른쪽 줄 두 번째)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>U-12</t>
+          <t>U-11</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>지도 · 광화문 실마리 곳</t>
+          <t>지도 · 근정전 앞마당</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>조작키 바로 위 가운데 한 줄(U-03 자리) — 마지막 문제를 맞혀 낙관(L-01)이 찍힌 뒤</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 분홍 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>모든 실마리를 풀었습니다. 이제 사정문으로 이동하세요.</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+          <t>🙋 2026-09-23 "초안 그대로 하자." · HANDOFF 🟩 기6 · 실마리가 남은 아이에게만 뜬다</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>U-13</t>
+          <t>U-12</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 지팡이를 든 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 분홍 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>U-14</t>
+          <t>U-13</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 파란 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 지팡이를 든 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2810,22 +2810,22 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>U-15</t>
+          <t>U-14</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>지도 · 홍례문 실마리 곳</t>
+          <t>지도 · 광화문 실마리 곳</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 파란 치마를 입은 사람에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>U-16</t>
+          <t>U-15</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 남색 치마를 입은 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2864,7 +2864,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>U-17</t>
+          <t>U-16</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 남색 치마를 입은 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2891,22 +2891,22 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>U-18</t>
+          <t>U-17</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>지도 · 영제교 실마리 곳</t>
+          <t>지도 · 홍례문 실마리 곳</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>U-19</t>
+          <t>U-18</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>U-20</t>
+          <t>U-19</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2972,7 +2972,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>U-21</t>
+          <t>U-20</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 개울가에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -2999,22 +2999,22 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>U-22</t>
+          <t>U-21</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>지도 · 근정문 실마리 곳</t>
+          <t>지도 · 영제교 실마리 곳</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 개울가에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3026,7 +3026,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>U-23</t>
+          <t>U-22</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3053,7 +3053,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>U-24</t>
+          <t>U-23</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 파란 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 나란히 선 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3080,7 +3080,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>U-25</t>
+          <t>U-24</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 파란 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>U-26</t>
+          <t>U-25</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 5번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 5</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 초록 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3134,22 +3134,22 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>U-27</t>
+          <t>U-26</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>지도 · 사정문 실마리 곳</t>
+          <t>지도 · 근정문 실마리 곳</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 5번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 5</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 아래 남색 치마를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>U-28</t>
+          <t>U-27</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 1번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 1</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>오른쪽 아래 남색 치마를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>U-29</t>
+          <t>U-28</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 2번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 2</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+          <t>왼쪽 아래 빨간 관복을 입은 관리에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3215,25 +3215,52 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
+          <t>U-29</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>지도 · 사정문 실마리 곳</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 3번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 3</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>오른쪽 담장에 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
           <t>U-30</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>지도 · 사정문 실마리 곳</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>가운데 안내문(뒤 딤 · 닫기 B-08) — 이 문의 4번째 실마리를 누르고 지도로 돌아왔을 때 · 곳 4</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>왼쪽 노란 저고리를 입은 두 궁녀에게 가까이 다가가면 실마리를 찾을 수 있습니다.</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>🙋 2026-09-25 "좋아. 그럼 이대로 할게." · HANDOFF 🟩 기2 · 틀은 U-05와 같다(사람은 「에게」, 담장·개울가는 「에」) · 같은 지도의 다음 판도 같은 곳을 다시 쓴다 · 실마리를 다시 누르면 못 간 그 곳을 다시 안내</t>
         </is>
